--- a/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/NWG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="92">
   <si>
     <t>NWG</t>
   </si>
@@ -656,231 +656,237 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5790100</v>
+      </c>
+      <c r="E8" s="3">
         <v>5380900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5636600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5617400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5222600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4898000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4706000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4689700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4681100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4271400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4341000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3977000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4699400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4708500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5309200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4275200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3572800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3014700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2971800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2852600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2776200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2672900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>11590100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3064400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3268100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3571300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3956400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4133500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3853200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3657400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3731200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3671800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -977,53 +983,56 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5790100</v>
+      </c>
+      <c r="E10" s="3">
         <v>5380900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5636600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5617400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5222600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4898000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4706000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4689700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4681100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4271400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4341000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3977000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4699400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4708500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1075,8 +1084,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1123,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1209,8 +1222,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1307,53 +1323,56 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E14" s="3">
         <v>19800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16100</v>
       </c>
-      <c r="G14" s="3">
-        <v>101400</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="H14" s="3">
+        <v>161700</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>191500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>55000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>97300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>30300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>140100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>163500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>66100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>69300</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1405,106 +1424,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>346300</v>
+      </c>
+      <c r="E15" s="3">
         <v>123100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>125500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>132400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>349400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>127300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>123300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>131300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>287500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>123800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>124800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>113800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>264300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>115400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-288700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-255900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-275400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-244400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-392900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-246900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-249200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-240100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-1080000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-236700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-323300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-256900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-440500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-328300</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-517700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-324900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-247000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-272100</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1536,204 +1561,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2718600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2676600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2983800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2666900</v>
       </c>
-      <c r="G17" s="3">
-        <v>2692100</v>
-      </c>
       <c r="H17" s="3">
+        <v>2631900</v>
+      </c>
+      <c r="I17" s="3">
         <v>2556900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2646600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2391100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2436600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2561300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2599700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2188000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2382700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2390100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1734700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1213100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>633700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>455300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>78600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>259300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-163400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>374800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6450400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1024700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>3458400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2053900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1396500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1596200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1472100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1065100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>879600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1143800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3071500</v>
+      </c>
+      <c r="E18" s="3">
         <v>2704300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2652800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2950500</v>
       </c>
-      <c r="G18" s="3">
-        <v>2530500</v>
-      </c>
       <c r="H18" s="3">
+        <v>2590800</v>
+      </c>
+      <c r="I18" s="3">
         <v>2341100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2059400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2298600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2244500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1710100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1741200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1789000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2316700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2318400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3574400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3062100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2939100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2559400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2893200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2593300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2939500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>2298100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5139700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>2039700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-190300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1517500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2559800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2537300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2381100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2592200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>2851600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2528000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1768,8 +1800,9 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1812,107 +1845,110 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1703200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1672500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1185800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1040900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2088500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1382300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1222300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1261500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5708700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1606600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1490000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-826600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-451400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2548600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-72800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1243500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2096100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1258700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3417800</v>
+      </c>
+      <c r="E21" s="3">
         <v>2827500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2778300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3082900</v>
       </c>
-      <c r="G21" s="3">
-        <v>2879800</v>
-      </c>
       <c r="H21" s="3">
+        <v>2940100</v>
+      </c>
+      <c r="I21" s="3">
         <v>2468400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2182700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2430000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2532000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1833800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1866100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1902800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2581000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2433800</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1964,8 +2000,11 @@
       <c r="AH21" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2008,8 +2047,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2062,204 +2101,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3031700</v>
+      </c>
+      <c r="E23" s="3">
         <v>2684500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2611000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2934400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2429100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2341100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1867900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2243700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2147200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1679800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1601100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1625500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2250600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2249100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1871200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1389700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1753300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1518500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>804700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1211000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1717200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1036600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-569000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>433100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-1680300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>690800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2108400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2308300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>1348700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>755500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1269300</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E24" s="3">
         <v>694600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>621800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>674800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>601500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>608500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>291700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>577700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>583900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>428100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>461300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>697700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>633400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>60400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>555400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>521500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>478900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>296500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>409500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>237300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>272900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>87500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>252500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-516200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>250200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>284400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-30200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>287600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>155900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>503200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2356,204 +2404,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2219700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1990000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1989200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2259600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1827600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1732600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1576200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1666000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1563300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1251600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1607500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1164200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1552900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1615700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1810800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>834300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1231700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1039600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>508200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>801600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1479900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>763700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-656500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>180500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-1164100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>440600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2058000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-295800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2338500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1061100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>599600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>766100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2126800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1890900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1874800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2148000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1693400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1617600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1562400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1570800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1492500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1159400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1565400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1056800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1296200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1582300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1729500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>746000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1150100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>965200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>427100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>714700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>1318900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>654800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-1033900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>74400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>383400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1922900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-445800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1827700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>941300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>541500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2650,8 +2707,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2671,64 +2731,64 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>86400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1300</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>19000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-5100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>33100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-36600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-181700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>43300</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-73500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-506700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>188700</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>78200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>122900</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>121600</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>138300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>71400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>143100</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC29" s="3">
         <v>0</v>
@@ -2748,8 +2808,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2846,8 +2909,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2944,8 +3010,11 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2988,160 +3057,166 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>1703200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1672500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1185800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1040900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2088500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1382300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1222300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1261500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5708700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1606600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1490000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>826600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>451400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2548600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>72800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1243500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2096100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1258700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2227700</v>
+      </c>
+      <c r="E33" s="3">
         <v>1987300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1987900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2258200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1824900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1733900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1663800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1668700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1579700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1235200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1641900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1131200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1372500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1657800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1656000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>239300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1338900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1043300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>550000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>836300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>1457200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>726200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-890700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>74400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>383400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1922900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-445800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1827700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>941300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>541500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3238,209 +3313,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2227700</v>
+      </c>
+      <c r="E35" s="3">
         <v>1987300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1987900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2258200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1824900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1733900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1663800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1668700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1579700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1235200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1641900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1131200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1372500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1657800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1656000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>239300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1338900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1043300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>550000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>836300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>1457200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>726200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-890700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>74400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>383400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1922900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-445800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1827700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>941300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>541500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3475,8 +3559,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3511,248 +3596,255 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>111563000</v>
+      </c>
+      <c r="E41" s="3">
         <v>115525400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>124745600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>124594700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>134380100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>136873900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>126557100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>150611200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>153938600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>218803200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>145536800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>156254100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>165304800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>162425800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>199416300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>210905300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>242515100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>218154500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>235006800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>216025800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>190428300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>172867500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>155485100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>144255600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>147635500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>120319500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>120759500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>136829800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>135005200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>128935400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>134514500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>163947000</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>190930100</v>
+      </c>
+      <c r="E42" s="3">
         <v>212607900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>182288000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>203751600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>210687800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>189156200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>194402600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>198740100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>165484600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>115250400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>181791700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>195519000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>181010500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>187574200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>190429100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>254431300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>223073600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>204653100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>209480900</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>211093600</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>214354900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>220805300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>278588300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>286836300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>333485700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>386787000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>309272100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>378350900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>317149200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>297141900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>275342400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>214471200</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>95600</v>
       </c>
-      <c r="F43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3">
         <v>8800</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N43" s="3">
         <v>62400</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -3805,8 +3897,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3849,8 +3944,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3903,53 +3998,56 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>308200</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>8679300</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>80100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10739700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1020500</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3">
         <v>1322800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>18556100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7772900</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4001,53 +4099,56 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>302493000</v>
+      </c>
+      <c r="E46" s="3">
         <v>328133300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>311134600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>328346400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>353747100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>326030100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>325749600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>349372700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>330162900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>335074100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>333206800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>353095900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>364871500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>357772900</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4099,53 +4200,56 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>114836100</v>
+      </c>
+      <c r="E47" s="3">
         <v>110235600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>107526200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>96237600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>98358700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>82595400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>80039300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>83507600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>66480500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>63506300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>65765300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>57024100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>45133500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>39453400</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -4197,68 +4301,71 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>5763100</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>4966400</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>5384200</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>5563700</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>5360700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
@@ -4277,124 +4384,130 @@
       <c r="AB48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>6720800</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AE48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF48" s="3">
         <v>1785100</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AG48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH48" s="3">
         <v>5746800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5609400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
         <v>9539100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9814300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10050500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10293200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>9737900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>9499600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>10170200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9592200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9596100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>9698400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>9170700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>9471200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>8871500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9337600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8907400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>8758700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8403800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8520100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>8341900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7982700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7807900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>7872200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>8051300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>8606300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>8810600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9031000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9404800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9105600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8808500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8738300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8692100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4491,8 +4604,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4589,68 +4705,71 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>37546800</v>
+      </c>
+      <c r="E52" s="3">
         <v>21997700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3441500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27721300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>22657900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>22836200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4853700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26442800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>18357800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>24471400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12807600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>23644800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25474300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>18428300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>9003000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15622800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>18089800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11444500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11424700</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
@@ -4666,8 +4785,8 @@
       <c r="AA52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB52" s="3">
-        <v>0</v>
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC52" s="3">
         <v>0</v>
@@ -4678,17 +4797,20 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AF52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH52" s="3">
         <v>3719300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2619100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4785,106 +4907,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>988943900</v>
+      </c>
+      <c r="E54" s="3">
         <v>989879900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>961713300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>975394500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1001202900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>917365900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>886344000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>954157600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>872443000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>880865900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>882296100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>875138500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>892860700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>860580000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>944853500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1025598500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1028340100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>974364800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>991018500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>965687300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>925218400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>901638600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>945717900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>965625300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1051849800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1088365900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>986073400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1098842800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1002248800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>957457700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>916938600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>950820900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4919,8 +5047,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4955,53 +5084,54 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>659380400</v>
+      </c>
+      <c r="E57" s="3">
         <v>649857100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>618829100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>643922900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>649288900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>604228700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>567652800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>616988300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>565555400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>559461000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>561579700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>548567300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>563957800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>558463200</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -5053,53 +5183,56 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76805100</v>
+      </c>
+      <c r="E58" s="3">
         <v>80476200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>142157500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>74637700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>91753700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>74233500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>136755300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>85956300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>119277900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>92356500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>137345200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>112057900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>140188800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>91263400</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5151,53 +5284,56 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>84572100</v>
+      </c>
+      <c r="E59" s="3">
         <v>95072700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>59354000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>95455300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>98202500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>90390100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>62585000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100075100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>81594100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>89346800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70773700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>89356400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>88476400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>83635200</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
       <c r="R59" s="3">
         <v>0</v>
       </c>
@@ -5240,62 +5376,65 @@
       <c r="AE59" s="3">
         <v>0</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AF59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH59" s="3">
         <v>7039800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>7399100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>820757600</v>
+      </c>
+      <c r="E60" s="3">
         <v>825405900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>822157500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>814015900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>839245100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>768852300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>768686900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>803019700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>766427400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>741164200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>771495900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>749981700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>792623000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>733361800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -5347,151 +5486,157 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>105052400</v>
+      </c>
+      <c r="E61" s="3">
         <v>101486200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>67170900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>99161200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>99341000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>89030900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>52852500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>94117400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>53684600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>85663900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>49323600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>76284400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>50977900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>73955900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>75165400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>68442500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>73759400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>69504600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>73192900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>70144900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>67336300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>60697900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>65973900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>72358400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>84759400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>78226100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>75279800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>81663200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>79910000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>69306000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>66392200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>65257600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4983400</v>
+      </c>
+      <c r="E62" s="3">
         <v>5321500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>14219400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>5249100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>5107500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5726200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14789000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5366600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4859300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6186100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>13290400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5603700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5038700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6602600</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -5534,17 +5679,20 @@
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH62" s="3">
         <v>4786500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>7729300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5641,8 +5789,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5739,8 +5890,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5837,106 +5991,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>930793400</v>
+      </c>
+      <c r="E66" s="3">
         <v>932213600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>904360700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>918426200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>943693700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>863609300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>837045700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>902503700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>824971200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>833014200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>834927700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>831869800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>848639600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>813920200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>896974000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>980883800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>979099600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>925689800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>938050400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>913727600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>872897000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>851642900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>893835900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>912940200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>995661200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1029580600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>926684400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1036394000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>938778600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>896037500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>856531000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>887586700</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5971,8 +6131,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6069,8 +6230,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6167,8 +6331,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6176,11 +6343,11 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>700</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -6188,11 +6355,11 @@
         <v>0</v>
       </c>
       <c r="I70" s="3">
+        <v>0</v>
+      </c>
+      <c r="J70" s="3">
         <v>600</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -6200,11 +6367,11 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3">
         <v>600</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -6265,8 +6432,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6363,106 +6533,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23845000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24200300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19406500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>21101200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>17370900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16421400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14304500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15004700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13372200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14291800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13559100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11913900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12169100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13572600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>29591400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>25294100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>29902400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27370100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31136300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>29426800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>28533200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>26792300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>27736600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>29219000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>31052800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>35865200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>33858800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>33317300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>35242900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>34094500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>33274700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>36591200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6559,8 +6735,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6657,8 +6836,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6755,106 +6937,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>58137200</v>
+      </c>
+      <c r="E76" s="3">
         <v>57645200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>57333100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>56942800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>57484600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53735800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>49262600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>51599000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>47418700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>47801200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>47328300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>43223600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>44170200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>46648600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>47879600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>44714700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>49240500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>48674900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>52968100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>51959700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>52321400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>49995800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>51882000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>52685000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>56188600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>58785400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>59389000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>62448800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>63470200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>61420100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>60407700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>63234100</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6951,209 +7139,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2227700</v>
+      </c>
+      <c r="E81" s="3">
         <v>1987300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1987900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2258200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1824900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1733900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1663800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1668700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1579700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1235200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1641900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1131200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1372500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1657800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1656000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>239300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1338900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1043300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>550000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>836300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>1457200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>726200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-890700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>74400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-1294500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>383400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1922900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-445800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1827700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>941300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>541500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>591700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7188,8 +7385,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7232,8 +7430,8 @@
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -7286,8 +7484,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7384,8 +7585,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7482,8 +7686,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7580,8 +7787,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7678,8 +7888,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7776,8 +7989,11 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7820,35 +8036,35 @@
       <c r="P89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>5</v>
@@ -7856,8 +8072,8 @@
       <c r="AB89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD89" s="3">
         <v>0</v>
@@ -7874,8 +8090,11 @@
       <c r="AH89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7910,8 +8129,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7954,8 +8174,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -8008,8 +8228,11 @@
       <c r="AH91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8106,8 +8329,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8204,8 +8430,11 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8248,35 +8477,35 @@
       <c r="P94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>5</v>
@@ -8284,8 +8513,8 @@
       <c r="AB94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD94" s="3">
         <v>0</v>
@@ -8302,8 +8531,11 @@
       <c r="AH94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8338,8 +8570,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8382,8 +8615,8 @@
       <c r="P96" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -8436,8 +8669,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8534,8 +8770,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8632,8 +8871,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8730,8 +8972,11 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8774,35 +9019,35 @@
       <c r="P100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>5</v>
@@ -8810,8 +9055,8 @@
       <c r="AB100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD100" s="3">
         <v>0</v>
@@ -8828,8 +9073,11 @@
       <c r="AH100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8872,35 +9120,35 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>5</v>
@@ -8908,8 +9156,8 @@
       <c r="AB101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD101" s="3">
         <v>0</v>
@@ -8926,8 +9174,11 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8970,35 +9221,35 @@
       <c r="P102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
+        <v>0</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>5</v>
@@ -9006,8 +9257,8 @@
       <c r="AB102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD102" s="3">
         <v>0</v>
@@ -9022,6 +9273,9 @@
         <v>0</v>
       </c>
       <c r="AH102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="3">
         <v>0</v>
       </c>
     </row>
